--- a/planning_report_output.xlsx
+++ b/planning_report_output.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Calculation" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Projections" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -841,7 +842,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MGW</t>
+          <t>vMGW</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -851,11 +852,11 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Peak Licensed Traffic</t>
+          <t>License Usage (%)</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>24599</v>
+        <v>45</v>
       </c>
     </row>
     <row r="23">
@@ -866,7 +867,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LMB</t>
+          <t>LL</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -875,47 +876,433 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>45</v>
+        <v>58</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HLR Subscribers</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>9324580</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>AuC Subscribers</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>9324580</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>VLR LMB (new MSC)</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2133103</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>VLR LLW (new MSC)</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2149249</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>UMG TRAFFIC LMB</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>UMG TAXI TRAFFIC LLW</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2G PDP(per sub) LIMBE</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>17234</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2G PDP(per sub) LILONGWE</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>15718</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2G SAU (per sub) LIMBE</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>48618</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2G SAU (per K sub) LILONGWE</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>36527</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>3G PDP(per sub) LIMBE</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>53493</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>3G PDP(per sub) LILONGWE</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>48997</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>3G SAU (per sub) LIMBE</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>104504</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>3G SAU (per sub) LILONGWE</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>86788</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>4G PDP(per sub) LIMBE</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>526980</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>4G PDP(per sub) LILONGWE</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>530784</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>4G SAU (per sub) LIMBE</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>518571</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>4G SAU (per sub) LILONGWE</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>519058</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>UGW PDP 2G&amp;3G (Per sub) LIMBE</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>68527</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>UGW PDP 4G (Per sub) LIMBE</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>536061</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>UGW THROUGHPUT( MBps) LIMBE</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>6402.84</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>UGW THROUGHPUT( MBps) LILONGWE</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>7039.29</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MGW</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>LL</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Peak Licensed Traffic</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>21033</v>
+          <t>CUPS PDP LMB</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>604588</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>vMGW</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>LL</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>License Usage (%)</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
+          <t>CUPS PDP LLW</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>617734</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>PCRF (PDP) LMB</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>593191</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>PCRF (PDP) LL</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>598229</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>LMB vMGW Traffic</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>LLW vMGW Traffic</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
         <v>58</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>SMSC/USSD TPS</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>HLR Hardware Capacity</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>10000000</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>UGW Throughput capacity LMB</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>UGW Throughput capacity LLW</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>MGW Capacity LMB</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>MGW Capacity LLW</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>VLR capacity</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>3300000</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>USN PDP capacity</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>10000000</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>LMB Aggregate Voice Traffic</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>40331</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>LLW Aggregate Voice Traffic</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>37815</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>LMB Aggregate Voice Traffic capacity</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>LLW Aggregate Voice Traffic capacity</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>50000</v>
       </c>
     </row>
   </sheetData>

--- a/planning_report_output.xlsx
+++ b/planning_report_output.xlsx
@@ -548,7 +548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -557,6 +557,7 @@
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -597,6 +598,11 @@
           <t>SGi UGW (MB/s)</t>
         </is>
       </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -615,6 +621,7 @@
       <c r="D3" s="6" t="n"/>
       <c r="E3" s="6" t="n"/>
       <c r="F3" s="6" t="n"/>
+      <c r="G3" s="6" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n"/>
@@ -629,6 +636,7 @@
       <c r="D4" s="10" t="n"/>
       <c r="E4" s="10" t="n"/>
       <c r="F4" s="10" t="n"/>
+      <c r="G4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n"/>
@@ -643,6 +651,7 @@
       <c r="D5" s="6" t="n"/>
       <c r="E5" s="6" t="n"/>
       <c r="F5" s="6" t="n"/>
+      <c r="G5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n"/>
@@ -657,6 +666,7 @@
       <c r="D6" s="10" t="n"/>
       <c r="E6" s="10" t="n"/>
       <c r="F6" s="10" t="n"/>
+      <c r="G6" s="10" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n"/>
@@ -671,6 +681,7 @@
       <c r="D7" s="6" t="n"/>
       <c r="E7" s="6" t="n"/>
       <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="n"/>
@@ -685,6 +696,7 @@
       <c r="D8" s="10" t="n"/>
       <c r="E8" s="10" t="n"/>
       <c r="F8" s="10" t="n"/>
+      <c r="G8" s="10" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -703,6 +715,7 @@
       </c>
       <c r="E9" s="6" t="n"/>
       <c r="F9" s="6" t="n"/>
+      <c r="G9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n"/>
@@ -717,6 +730,7 @@
       </c>
       <c r="E10" s="10" t="n"/>
       <c r="F10" s="10" t="n"/>
+      <c r="G10" s="10" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n"/>
@@ -731,6 +745,7 @@
       </c>
       <c r="E11" s="6" t="n"/>
       <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n"/>
@@ -745,6 +760,7 @@
       </c>
       <c r="E12" s="10" t="n"/>
       <c r="F12" s="10" t="n"/>
+      <c r="G12" s="10" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n"/>
@@ -759,6 +775,7 @@
       </c>
       <c r="E13" s="6" t="n"/>
       <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="11" t="n"/>
@@ -773,6 +790,7 @@
       </c>
       <c r="E14" s="10" t="n"/>
       <c r="F14" s="10" t="n"/>
+      <c r="G14" s="10" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -791,6 +809,7 @@
       </c>
       <c r="E15" s="6" t="n"/>
       <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n"/>
@@ -805,6 +824,7 @@
       </c>
       <c r="E16" s="10" t="n"/>
       <c r="F16" s="10" t="n"/>
+      <c r="G16" s="10" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="11" t="n"/>
@@ -821,6 +841,7 @@
       <c r="F17" s="12" t="n">
         <v>5869.84</v>
       </c>
+      <c r="G17" s="6" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -839,6 +860,7 @@
       </c>
       <c r="E18" s="10" t="n"/>
       <c r="F18" s="10" t="n"/>
+      <c r="G18" s="10" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n"/>
@@ -853,6 +875,7 @@
       </c>
       <c r="E19" s="6" t="n"/>
       <c r="F19" s="6" t="n"/>
+      <c r="G19" s="6" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="11" t="n"/>
@@ -869,6 +892,7 @@
       <c r="F20" s="13" t="n">
         <v>6500.29</v>
       </c>
+      <c r="G20" s="10" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -881,12 +905,13 @@
           <t>UPCF PDP LMB</t>
         </is>
       </c>
-      <c r="C21" s="5" t="n">
-        <v>593191</v>
-      </c>
+      <c r="C21" s="6" t="n"/>
       <c r="D21" s="6" t="n"/>
       <c r="E21" s="6" t="n"/>
       <c r="F21" s="6" t="n"/>
+      <c r="G21" s="5" t="n">
+        <v>593191</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="n"/>
@@ -896,11 +921,12 @@
         </is>
       </c>
       <c r="C22" s="10" t="n"/>
-      <c r="D22" s="9" t="n">
-        <v>598229</v>
-      </c>
+      <c r="D22" s="10" t="n"/>
       <c r="E22" s="10" t="n"/>
       <c r="F22" s="10" t="n"/>
+      <c r="G22" s="9" t="n">
+        <v>598229</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -913,12 +939,13 @@
           <t>Traffic (Erlangs) LMB</t>
         </is>
       </c>
-      <c r="C23" s="5" t="n">
-        <v>24599</v>
-      </c>
+      <c r="C23" s="6" t="n"/>
       <c r="D23" s="6" t="n"/>
       <c r="E23" s="6" t="n"/>
       <c r="F23" s="6" t="n"/>
+      <c r="G23" s="5" t="n">
+        <v>24599</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="n"/>
@@ -928,11 +955,12 @@
         </is>
       </c>
       <c r="C24" s="10" t="n"/>
-      <c r="D24" s="9" t="n">
-        <v>21033</v>
-      </c>
+      <c r="D24" s="10" t="n"/>
       <c r="E24" s="10" t="n"/>
       <c r="F24" s="10" t="n"/>
+      <c r="G24" s="9" t="n">
+        <v>21033</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -945,12 +973,13 @@
           <t>Traffic (Erlangs) LMB</t>
         </is>
       </c>
-      <c r="C25" s="5" t="n">
-        <v>45</v>
-      </c>
+      <c r="C25" s="6" t="n"/>
       <c r="D25" s="6" t="n"/>
       <c r="E25" s="6" t="n"/>
       <c r="F25" s="6" t="n"/>
+      <c r="G25" s="5" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="11" t="n"/>
@@ -960,18 +989,19 @@
         </is>
       </c>
       <c r="C26" s="10" t="n"/>
-      <c r="D26" s="9" t="n">
-        <v>58</v>
-      </c>
+      <c r="D26" s="10" t="n"/>
       <c r="E26" s="10" t="n"/>
       <c r="F26" s="10" t="n"/>
+      <c r="G26" s="9" t="n">
+        <v>58</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="A1:G1"/>
     <mergeCell ref="A9:A14"/>
     <mergeCell ref="A3:A8"/>
     <mergeCell ref="A25:A26"/>
-    <mergeCell ref="A1:F1"/>
     <mergeCell ref="A15:A17"/>
     <mergeCell ref="A23:A24"/>
     <mergeCell ref="A18:A20"/>
